--- a/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="106">
   <si>
     <t>TC ID</t>
   </si>
@@ -282,6 +282,69 @@
   </si>
   <si>
     <t>${TC001.Lease End Date}</t>
+  </si>
+  <si>
+    <t>FPJ50N</t>
+  </si>
+  <si>
+    <t>BYD DOLPHIN</t>
+  </si>
+  <si>
+    <t>8956</t>
+  </si>
+  <si>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Shakya</t>
+  </si>
+  <si>
+    <t>27 Jun 1986</t>
+  </si>
+  <si>
+    <t>333665987</t>
+  </si>
+  <si>
+    <t>sudeep.shakya@outlook.com.test</t>
+  </si>
+  <si>
+    <t>QBE Management Services Pty Ltd</t>
+  </si>
+  <si>
+    <t>REQ-167</t>
+  </si>
+  <si>
+    <t>Cancel Fuel Card</t>
+  </si>
+  <si>
+    <t>30 Jul 2026 05:29 PM</t>
+  </si>
+  <si>
+    <t>CYP806</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>4981</t>
+  </si>
+  <si>
+    <t>Neeti</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>03 Jul 1993</t>
+  </si>
+  <si>
+    <t>0499656877</t>
+  </si>
+  <si>
+    <t>neeti.tripathi@kmart.com.au.test</t>
+  </si>
+  <si>
+    <t>Kmart Australia Limited</t>
   </si>
 </sst>
 </file>
@@ -1298,27 +1361,27 @@
   <dimension ref="A1:AN10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.7" customWidth="1"/>
-    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.775" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.775" customWidth="1"/>
-    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="23.775" customWidth="1"/>
-    <col min="11" max="11" width="17.225" customWidth="1"/>
-    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
-    <col min="23" max="23" width="20.7" customWidth="1"/>
-    <col min="24" max="24" width="24.6" customWidth="1"/>
-    <col min="25" max="25" width="29.8" customWidth="1"/>
-    <col min="26" max="27" width="24.5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
+    <col min="2" max="2" customWidth="true" width="20.7"/>
+    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
+    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
+    <col min="6" max="6" customWidth="true" width="16.775"/>
+    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
+    <col min="8" max="8" customWidth="true" width="21.775"/>
+    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
+    <col min="10" max="10" customWidth="true" width="23.775"/>
+    <col min="11" max="11" customWidth="true" width="17.225"/>
+    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
+    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
+    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
+    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
+    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
+    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
+    <col min="18" max="22" customWidth="true" width="19.1083333333333"/>
+    <col min="23" max="23" customWidth="true" width="20.7"/>
+    <col min="24" max="24" customWidth="true" width="24.6"/>
+    <col min="25" max="25" customWidth="true" width="29.8"/>
+    <col min="26" max="27" customWidth="true" width="24.5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="69" spans="1:40">
@@ -1451,15 +1514,15 @@
         <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="6">
+        <v>99</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>53101</v>
-      </c>
-      <c r="E2" s="6">
+        <v>4982.0</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>53101</v>
+        <v>4982.0</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1495,11 +1558,11 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>53,101 km</v>
+        <v>4,982 km</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>45</v>
@@ -1508,51 +1571,51 @@
         <v>46</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AB2" s="7" t="s">
         <v>49</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>Neil Jones</v>
+        <v>Neeti Tripathi</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="AI2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v>MAZDA CX-5 - YKQ26Y</v>
+        <v>TESLA MODEL Y - CYP806</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="7" t="s">
         <v>59</v>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="112">
   <si>
     <t>TC ID</t>
   </si>
@@ -345,6 +345,25 @@
   </si>
   <si>
     <t>Kmart Australia Limited</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+18,065 km</t>
+  </si>
+  <si>
+    <t>BTFWULH</t>
+  </si>
+  <si>
+    <t>ABDGO</t>
+  </si>
+  <si>
+    <t>0469 000 000</t>
+  </si>
+  <si>
+    <t>191799@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>AMP Capital Office and Industrial Pty Ltd</t>
   </si>
 </sst>
 </file>
@@ -1514,15 +1533,15 @@
         <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="D2" s="6" t="e">
         <f>C2+1</f>
-        <v>4982.0</v>
-      </c>
-      <c r="E2" s="6" t="n">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E2" s="6" t="e">
         <f>D2</f>
-        <v>4982.0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1560,9 +1579,9 @@
       <c r="U2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="7" t="str">
+      <c r="V2" s="7" t="e">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>4,982 km</v>
+        <v>#VALUE!</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>45</v>
@@ -1583,29 +1602,29 @@
         <v>49</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>Neeti Tripathi</v>
+        <v>BTFWULH ABDGO</v>
       </c>
       <c r="AF2" s="7" t="s">
         <v>102</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AI2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/06_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="121">
   <si>
     <t>TC ID</t>
   </si>
@@ -364,6 +364,36 @@
   </si>
   <si>
     <t>AMP Capital Office and Industrial Pty Ltd</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,079 km</t>
+  </si>
+  <si>
+    <t>0469 000 111</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,201 km</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,028 km</t>
+  </si>
+  <si>
+    <t>ALFVU</t>
+  </si>
+  <si>
+    <t>ZZNXTGSP</t>
+  </si>
+  <si>
+    <t>0455 512 334</t>
+  </si>
+  <si>
+    <t>139638@omsrefresh.com</t>
+  </si>
+  <si>
+    <t>BHP Iron Ore Pty Ltd</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1563,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D2" s="6" t="e">
         <f>C2+1</f>
@@ -1602,29 +1632,29 @@
         <v>49</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>BTFWULH ABDGO</v>
+        <v>ALFVU ZZNXTGSP</v>
       </c>
       <c r="AF2" s="7" t="s">
         <v>102</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AI2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
